--- a/data/Study_dates_MeLiDos_UCR.xlsx
+++ b/data/Study_dates_MeLiDos_UCR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/WP2.2.5_Data_Analysis/SanchoEtAl_Dataset_2025/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/Sancho-SalasEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EAE983-BC3D-6041-B119-90CB5127301C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60EED61-0DD3-D54B-BB4A-4830E38DF272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1300" yWindow="620" windowWidth="38200" windowHeight="22880" xr2:uid="{5E03C250-4C67-44F6-BA87-C660DAF94A8E}"/>
   </bookViews>
@@ -53,12 +53,6 @@
     <t>date_consent</t>
   </si>
   <si>
-    <t>date_trial_start</t>
-  </si>
-  <si>
-    <t>date_trial_end</t>
-  </si>
-  <si>
     <t>comments</t>
   </si>
   <si>
@@ -345,6 +339,12 @@
   </si>
   <si>
     <t>UCR_S040_w</t>
+  </si>
+  <si>
+    <t>datetime_trial_start</t>
+  </si>
+  <si>
+    <t>datetime_trial_end</t>
   </si>
 </sst>
 </file>
@@ -796,18 +796,18 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4">
         <v>5397</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4">
         <v>4996</v>
@@ -853,7 +853,7 @@
     </row>
     <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4">
         <v>5467</v>
@@ -885,7 +885,7 @@
     </row>
     <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="4">
         <v>5399</v>
@@ -908,7 +908,7 @@
     </row>
     <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="4">
         <v>5179</v>
@@ -931,7 +931,7 @@
     </row>
     <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" s="4">
         <v>5501</v>
@@ -964,7 +964,7 @@
     </row>
     <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <v>5457</v>
@@ -985,12 +985,12 @@
         <v>45831.4375</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="4">
         <v>5237</v>
@@ -1011,12 +1011,12 @@
         <v>45831.4375</v>
       </c>
       <c r="H11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="4">
         <v>5379</v>
@@ -1037,7 +1037,7 @@
         <v>45831.4375</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -1051,7 +1051,7 @@
     </row>
     <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <v>5397</v>
@@ -1072,12 +1072,12 @@
         <v>45838.375</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="4">
         <v>4996</v>
@@ -1098,12 +1098,12 @@
         <v>45838.375</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B16" s="4">
         <v>5467</v>
@@ -1124,7 +1124,7 @@
         <v>45838.375</v>
       </c>
       <c r="H16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1138,7 +1138,7 @@
     </row>
     <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <v>5457</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <v>5237</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <v>5379</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B22" s="4">
         <v>5399</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B23" s="4">
         <v>5179</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" s="4">
         <v>5501</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B26" s="4">
         <v>5179</v>
@@ -1315,12 +1315,12 @@
         <v>45845.375</v>
       </c>
       <c r="H26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B27" s="4">
         <v>5501</v>
@@ -1341,7 +1341,7 @@
         <v>45845.375</v>
       </c>
       <c r="H27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1355,7 +1355,7 @@
     </row>
     <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B29" s="4">
         <v>5399</v>
@@ -1378,7 +1378,7 @@
     </row>
     <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B30" s="4">
         <v>5457</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="4">
         <v>5237</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="4">
         <v>5379</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B35" s="4">
         <v>5397</v>
@@ -1486,12 +1486,12 @@
         <v>45852.385416666664</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="4">
         <v>4996</v>
@@ -1512,7 +1512,7 @@
         <v>45852.385416666664</v>
       </c>
       <c r="H36" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1526,7 +1526,7 @@
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B38" s="4">
         <v>5399</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="4">
         <v>5379</v>
@@ -1581,7 +1581,7 @@
     </row>
     <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" s="4">
         <v>5237</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="4">
         <v>5457</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B44" s="4">
         <v>5179</v>
@@ -1657,12 +1657,12 @@
         <v>45852.604166666664</v>
       </c>
       <c r="H44" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B45" s="4">
         <v>5501</v>
@@ -1683,7 +1683,7 @@
         <v>45852.604166666664</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1697,7 +1697,7 @@
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B47" s="4">
         <v>5457</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B48" s="4">
         <v>6305</v>
@@ -1752,7 +1752,7 @@
     </row>
     <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B50" s="4">
         <v>6121</v>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="4">
         <v>4996</v>
@@ -1807,7 +1807,7 @@
     </row>
     <row r="53" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B53" s="4">
         <v>5237</v>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B54" s="4">
         <v>6132</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B56" s="4">
         <v>6115</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="57" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B57" s="4">
         <v>5397</v>
@@ -1917,7 +1917,7 @@
     </row>
     <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B59" s="4">
         <v>6111</v>
@@ -1938,12 +1938,12 @@
         <v>45866.375</v>
       </c>
       <c r="H59" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B60" s="4">
         <v>6837</v>
@@ -1964,7 +1964,7 @@
         <v>45866.375</v>
       </c>
       <c r="H60" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1978,7 +1978,7 @@
     </row>
     <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B62" s="4">
         <v>5399</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B63" s="4">
         <v>6253</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B65" s="4">
         <v>6679</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B66" s="4">
         <v>6359</v>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B68" s="4">
         <v>6306</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B69" s="4">
         <v>5237</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B71" s="4">
         <v>5397</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B72" s="4">
         <v>6305</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B74" s="4">
         <v>6132</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B75" s="4">
         <v>5457</v>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B77" s="4">
         <v>5237</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B78" s="4">
         <v>6359</v>
@@ -2308,7 +2308,7 @@
     </row>
     <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B80" s="4">
         <v>6306</v>
@@ -2331,7 +2331,7 @@
     </row>
     <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B81" s="4">
         <v>6253</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="83" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B83" s="4">
         <v>6111</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="84" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B84" s="4">
         <v>5399</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="86" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B86" s="4">
         <v>6837</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="87" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B87" s="4">
         <v>6679</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B89" s="4">
         <v>6115</v>
@@ -2494,12 +2494,12 @@
         <v>45887.673611111109</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B90" s="4">
         <v>6305</v>
@@ -2520,7 +2520,7 @@
         <v>45887.673611111109</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2535,7 +2535,7 @@
     </row>
     <row r="92" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B92" s="4">
         <v>5397</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B93" s="4">
         <v>6132</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B95" s="4">
         <v>4996</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B96" s="4">
         <v>6121</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="98" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B98" s="4">
         <v>6253</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="99" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B99" s="4">
         <v>6111</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="101" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B101" s="4">
         <v>5399</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="102" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B102" s="4">
         <v>6306</v>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="104" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B104" s="4">
         <v>6115</v>
@@ -2776,12 +2776,12 @@
         <v>45659.454861111109</v>
       </c>
       <c r="H104" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B105" s="4">
         <v>6121</v>
@@ -2802,7 +2802,7 @@
         <v>45659.454861111109</v>
       </c>
       <c r="H105" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2816,7 +2816,7 @@
     </row>
     <row r="107" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B107" s="4">
         <v>5237</v>
@@ -2837,12 +2837,12 @@
         <v>45902.611111111109</v>
       </c>
       <c r="H107" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B108" s="4">
         <v>6253</v>
@@ -2863,7 +2863,7 @@
         <v>45902.611111111109</v>
       </c>
       <c r="H108" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2877,7 +2877,7 @@
     </row>
     <row r="110" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B110" s="4">
         <v>6132</v>
@@ -2898,12 +2898,12 @@
         <v>45902.625</v>
       </c>
       <c r="H110" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B111" s="4">
         <v>6679</v>
@@ -2924,7 +2924,7 @@
         <v>45902.625</v>
       </c>
       <c r="H111" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2938,7 +2938,7 @@
     </row>
     <row r="113" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B113" s="4">
         <v>5397</v>
@@ -2959,12 +2959,12 @@
         <v>45902.625</v>
       </c>
       <c r="H113" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B114" s="4">
         <v>6359</v>
@@ -2985,7 +2985,7 @@
         <v>45902.625</v>
       </c>
       <c r="H114" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2999,7 +2999,7 @@
     </row>
     <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B116" s="4">
         <v>6111</v>
@@ -3020,12 +3020,12 @@
         <v>45902.625</v>
       </c>
       <c r="H116" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B117" s="4">
         <v>4996</v>
@@ -3046,7 +3046,7 @@
         <v>45902.625</v>
       </c>
       <c r="H117" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -3060,7 +3060,7 @@
     </row>
     <row r="119" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B119" s="4">
         <v>6305</v>
@@ -3081,12 +3081,12 @@
         <v>45902.625</v>
       </c>
       <c r="H119" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B120" s="4">
         <v>5457</v>
@@ -3107,7 +3107,7 @@
         <v>45902.625</v>
       </c>
       <c r="H120" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -3121,7 +3121,7 @@
     </row>
     <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B122" s="4">
         <v>5399</v>
@@ -3142,12 +3142,12 @@
         <v>45907.666666666664</v>
       </c>
       <c r="H122" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B123" s="4">
         <v>6306</v>
@@ -3168,7 +3168,7 @@
         <v>45907.666666666664</v>
       </c>
       <c r="H123" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -3213,6 +3213,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d5615116-53a2-4a32-b483-17fd8f718363" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004353A7D987A99049A03994972347A526" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="03c7f400289e08b5d91e724cfa88fd28">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ac8fea5-7947-4ae1-ad07-8eab2e73f7d8" xmlns:ns4="d5615116-53a2-4a32-b483-17fd8f718363" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="102708c53d96a796777b4b7fda7c83ee" ns3:_="" ns4:_="">
     <xsd:import namespace="8ac8fea5-7947-4ae1-ad07-8eab2e73f7d8"/>
@@ -3451,14 +3459,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d5615116-53a2-4a32-b483-17fd8f718363" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9546CEE-830D-4569-82E9-3186B101F743}">
   <ds:schemaRefs>
@@ -3468,6 +3468,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1976243-C543-44E5-81C6-44C0AB7DFC98}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d5615116-53a2-4a32-b483-17fd8f718363"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8C3D2E-2D20-4F27-AD77-9D3A85AF8FCF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3484,14 +3494,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1976243-C543-44E5-81C6-44C0AB7DFC98}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d5615116-53a2-4a32-b483-17fd8f718363"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/Study_dates_MeLiDos_UCR.xlsx
+++ b/data/Study_dates_MeLiDos_UCR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/Sancho-SalasEtAl_Dataset_2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60EED61-0DD3-D54B-BB4A-4830E38DF272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC072DC-783B-AB4A-A836-8CAE90C444C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1300" yWindow="620" windowWidth="38200" windowHeight="22880" xr2:uid="{5E03C250-4C67-44F6-BA87-C660DAF94A8E}"/>
+    <workbookView xWindow="61520" yWindow="2300" windowWidth="38200" windowHeight="22880" xr2:uid="{5E03C250-4C67-44F6-BA87-C660DAF94A8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -2773,7 +2773,7 @@
         <v>45894.614583333336</v>
       </c>
       <c r="G104" s="9">
-        <v>45659.454861111109</v>
+        <v>45901.454861111109</v>
       </c>
       <c r="H104" t="s">
         <v>84</v>
@@ -2799,7 +2799,7 @@
         <v>45894.614583333336</v>
       </c>
       <c r="G105" s="9">
-        <v>45659.454861111109</v>
+        <v>45901.454861111109</v>
       </c>
       <c r="H105" t="s">
         <v>84</v>
@@ -3204,20 +3204,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d5615116-53a2-4a32-b483-17fd8f718363" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d5615116-53a2-4a32-b483-17fd8f718363" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3460,19 +3460,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9546CEE-830D-4569-82E9-3186B101F743}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1976243-C543-44E5-81C6-44C0AB7DFC98}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d5615116-53a2-4a32-b483-17fd8f718363"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1976243-C543-44E5-81C6-44C0AB7DFC98}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9546CEE-830D-4569-82E9-3186B101F743}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d5615116-53a2-4a32-b483-17fd8f718363"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
